--- a/pregenerated_results/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
+++ b/pregenerated_results/att_iptw_gee_IPTW_GEE_workload_index_mgr.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.024</v>
+        <v>-0.066</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E7" t="n">
-        <v>0.022</v>
+        <v>0.059</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.046</v>
+        <v>0.227</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E8" t="n">
-        <v>0.045</v>
+        <v>0.225</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.392</v>
       </c>
       <c r="D9" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="F9" t="b">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.074</v>
+        <v>-0.401</v>
       </c>
       <c r="D10" t="n">
         <v>0.004</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.397</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -714,7 +714,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>-0.054</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.033</v>
+        <v>0.048</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -741,7 +741,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.023</v>
+        <v>0.077</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004</v>
+        <v>-0.001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.019</v>
+        <v>0.076</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -768,7 +768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="E13" t="n">
         <v>0.006</v>
@@ -795,7 +795,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.041</v>
+        <v>0.007</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="E14" t="n">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -822,7 +822,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -831,13 +831,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.032</v>
       </c>
       <c r="D15" t="n">
-        <v>0.007</v>
+        <v>-0.004</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.002</v>
+        <v>0.028</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -849,7 +849,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="D16" t="n">
         <v>-0.004</v>
       </c>
       <c r="E16" t="n">
-        <v>0.028</v>
+        <v>0.018</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.005</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="E17" t="n">
-        <v>0.012</v>
+        <v>-0.002</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -903,7 +903,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0.197</v>
       </c>
       <c r="D18" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="F18" t="b">
         <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -930,7 +930,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>-0.143</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.002</v>
+        <v>0.003</v>
       </c>
       <c r="E19" t="n">
-        <v>0.006</v>
+        <v>0.14</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -957,7 +957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -966,13 +966,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.077</v>
+        <v>0.034</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.076</v>
+        <v>0.033</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.019</v>
+        <v>-0</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>-0.019</v>
       </c>
       <c r="D22" t="n">
-        <v>0.003</v>
+        <v>-0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.11</v>
+        <v>0.019</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1038,7 +1038,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.197</v>
+        <v>-0.128</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="E23" t="n">
-        <v>0.191</v>
+        <v>0.126</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.143</v>
+        <v>-0.074</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="E24" t="n">
-        <v>0.14</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1092,7 +1092,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1101,16 +1101,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.107</v>
       </c>
       <c r="D25" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="E25" t="n">
-        <v>0.048</v>
+        <v>0.104</v>
       </c>
       <c r="F25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
@@ -1119,7 +1119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.128</v>
+        <v>-0.014</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="E26" t="n">
-        <v>0.126</v>
+        <v>0.012</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1155,16 +1155,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.227</v>
+        <v>0.046</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.225</v>
+        <v>0.045</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
@@ -1173,7 +1173,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.392</v>
+        <v>-0.041</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.384</v>
+        <v>0.04</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1200,7 +1200,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.401</v>
+        <v>0.041</v>
       </c>
       <c r="D29" t="n">
-        <v>0.005</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>0.396</v>
+        <v>0.032</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1227,7 +1227,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.107</v>
+        <v>-0.024</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.003</v>
+        <v>-0.002</v>
       </c>
       <c r="E30" t="n">
-        <v>0.104</v>
+        <v>0.022</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
         <v>1</v>
@@ -1254,7 +1254,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.041</v>
+        <v>0.023</v>
       </c>
       <c r="D31" t="n">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="E31" t="n">
-        <v>0.041</v>
+        <v>0.019</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -1281,7 +1281,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.066</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.059</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1317,18 +1317,45 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022</v>
+        <v>-0.113</v>
       </c>
       <c r="D33" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>baseline_workload</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>continuous</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E34" t="n">
         <v>-0.004</v>
       </c>
-      <c r="E33" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="b">
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1388,13 +1415,13 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>554.8319074166568</v>
+        <v>554.8278686969497</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07201588164977409</v>
+        <v>0.07201561406504584</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2496221955703657</v>
+        <v>0.249622252217613</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1464,19 +1491,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.036602236209995</v>
+        <v>2.036528116116089</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3595551986980818</v>
+        <v>0.3596477868739569</v>
       </c>
       <c r="D2" t="n">
-        <v>1.331886996307612</v>
+        <v>1.331631406723596</v>
       </c>
       <c r="E2" t="n">
-        <v>2.741317476112378</v>
+        <v>2.741424825508582</v>
       </c>
       <c r="F2" t="n">
-        <v>1.476888557171562e-08</v>
+        <v>1.491289234988775e-08</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1516,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0631356639061495</v>
+        <v>-0.06313217325344533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06889171256433489</v>
+        <v>0.06889056314771</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1981609393655314</v>
+        <v>-0.1981551958976392</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07188961155323242</v>
+        <v>0.07189084939074855</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3594320324412411</v>
+        <v>0.3594505811850852</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1541,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.1420900222427463</v>
+        <v>-0.1421216341086119</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1674834691504837</v>
+        <v>0.1674868395456608</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4703515897835195</v>
+        <v>-0.470389807502546</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1861715452980269</v>
+        <v>0.1861465392853222</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3962250586520981</v>
+        <v>0.3961294910286149</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1566,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1123402147235629</v>
+        <v>0.1122926771520418</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1386455160915385</v>
+        <v>0.1386453461258838</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1594000034338211</v>
+        <v>-0.1594472078787805</v>
       </c>
       <c r="E5" t="n">
-        <v>0.384080432880947</v>
+        <v>0.384032562182864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.41778537656363</v>
+        <v>0.4179818513531919</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1591,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2616157459576963</v>
+        <v>0.2616025743535587</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1491654091054355</v>
+        <v>0.1491669983391062</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03074308362814021</v>
+        <v>-0.03075937007303542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5539745755435328</v>
+        <v>0.5539645187801528</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07945392276127221</v>
+        <v>0.07947226102465754</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1616,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2268721888728756</v>
+        <v>0.2268312746455364</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1322971139673637</v>
+        <v>0.132298380564079</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.03242538976174825</v>
+        <v>-0.03246878647303231</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4861697675074994</v>
+        <v>0.4861313357641052</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08636928988307689</v>
+        <v>0.08642902979742563</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1641,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2700551131784784</v>
+        <v>0.2700445938356431</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1556352113937797</v>
+        <v>0.1556347708039218</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03498429587960766</v>
+        <v>-0.03499395168218966</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5750945222365644</v>
+        <v>0.5750831393534758</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08270891977837933</v>
+        <v>0.08272001866660153</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1666,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05428434711664003</v>
+        <v>0.0542711227097304</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1256761579998883</v>
+        <v>0.1256781786382992</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1920363962785064</v>
+        <v>-0.1920535810639273</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3006050905117864</v>
+        <v>0.3005958264833881</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6657862511070221</v>
+        <v>0.6658677797457505</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1691,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.249705205268261</v>
+        <v>0.2497438528462251</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1813103926938773</v>
+        <v>0.1813159454550471</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1056566344345526</v>
+        <v>-0.105628870068496</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6050670449710747</v>
+        <v>0.6051165757609462</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1684426953271453</v>
+        <v>0.1683898576946207</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1716,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.05406182499411179</v>
+        <v>-0.05404748715975852</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2032970913516045</v>
+        <v>0.2033019608685913</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4525168022050058</v>
+        <v>-0.4525120084485689</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3443931522167823</v>
+        <v>0.3444170341290519</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7902967967088366</v>
+        <v>0.7903560186733682</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1741,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1958077105120102</v>
+        <v>0.1958319998199368</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1454915101622135</v>
+        <v>0.1454956520450952</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08935040946227149</v>
+        <v>-0.08933423809562116</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4809658304862918</v>
+        <v>0.4809982377354948</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1783554160232452</v>
+        <v>0.1783139273714509</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1766,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2559736583242179</v>
+        <v>0.2559612663510776</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1734212677168909</v>
+        <v>0.1734197778580745</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.08392578055416705</v>
+        <v>-0.08393525245768513</v>
       </c>
       <c r="E13" t="n">
-        <v>0.595873097202603</v>
+        <v>0.5958577851598403</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1399379060136746</v>
+        <v>0.1399536847540253</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1791,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2621085393999598</v>
+        <v>0.2621481172649275</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1613185653416903</v>
+        <v>0.1613253603240469</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.05407003870742472</v>
+        <v>-0.05404377876315142</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5782871175073443</v>
+        <v>0.5783400132930063</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1042076460090699</v>
+        <v>0.1041699465492034</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1816,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1217698113596888</v>
+        <v>0.1218499733769809</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1773010282590537</v>
+        <v>0.1773004908031792</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2257338184499747</v>
+        <v>-0.2256526030385254</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4692734411693524</v>
+        <v>0.4693525497924873</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4922106710207487</v>
+        <v>0.4919244509941078</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1841,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0945284917309256</v>
+        <v>-0.09451528971236253</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1774418821294875</v>
+        <v>0.1774443081578673</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4423081900537226</v>
+        <v>-0.4422997429634093</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2532512065918714</v>
+        <v>0.2532691635386843</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5942209726114982</v>
+        <v>0.5942775264683451</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1866,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1837143702306886</v>
+        <v>0.1837929126314662</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1637040102408058</v>
+        <v>0.163703525416397</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1371395939660669</v>
+        <v>-0.1370601013269093</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5045683344274441</v>
+        <v>0.5046459265898418</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2617625340704789</v>
+        <v>0.2615572341094268</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1891,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.06981748387247649</v>
+        <v>-0.06979157770297553</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1930840620841175</v>
+        <v>0.193090244427888</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4482552915460427</v>
+        <v>-0.4482415025476718</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3086203238010897</v>
+        <v>0.3086583471417207</v>
       </c>
       <c r="F18" t="n">
-        <v>0.717657595268157</v>
+        <v>0.7177665256766774</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1916,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1969655303245182</v>
+        <v>0.1969435449344519</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1779209025639873</v>
+        <v>0.1779269841509344</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1517530307977571</v>
+        <v>-0.1517869358792084</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5456840914467934</v>
+        <v>0.5456740257481123</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2682766969715222</v>
+        <v>0.2683464829921536</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1941,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1322032620606821</v>
+        <v>0.1321940896671349</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1728217080449772</v>
+        <v>0.1728218867405858</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2065210614541692</v>
+        <v>-0.2065305840846736</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4709275855755335</v>
+        <v>0.4709187634189435</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4442899600438317</v>
+        <v>0.4443220366035914</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1966,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1411989312213749</v>
+        <v>0.141231046250707</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1536032454395495</v>
+        <v>0.1536097423531369</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1598578977486085</v>
+        <v>-0.1598385164359182</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4422557601913583</v>
+        <v>0.4423006089373323</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3579677249886023</v>
+        <v>0.3578787337224097</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1991,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.03228862083243202</v>
+        <v>-0.03228391789157729</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1700096908231726</v>
+        <v>0.1700133157503022</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3655014918686401</v>
+        <v>-0.3655038936544058</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3009242502037761</v>
+        <v>0.3009360578712512</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8493700668133831</v>
+        <v>0.8493949168477309</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +2016,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2528578615211169</v>
+        <v>0.2528831528792491</v>
       </c>
       <c r="C23" t="n">
-        <v>0.170788251243906</v>
+        <v>0.1707936085192126</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.08188095989951694</v>
+        <v>-0.08186616860804097</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5875966829417508</v>
+        <v>0.5876324743665391</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1387307179459428</v>
+        <v>0.1387036162854039</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2041,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1009814874983659</v>
+        <v>0.1009950565062645</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1174236802772657</v>
+        <v>0.1174249770083671</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1291646967772211</v>
+        <v>-0.1291536693155789</v>
       </c>
       <c r="E24" t="n">
-        <v>0.331127671773953</v>
+        <v>0.3311437823281078</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3898025510379947</v>
+        <v>0.3897440894661861</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2066,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.004330053901152394</v>
+        <v>0.004336472015973053</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08182631997408578</v>
+        <v>0.08182753702008566</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1560465862355062</v>
+        <v>-0.1560425534870128</v>
       </c>
       <c r="E25" t="n">
-        <v>0.164706694037811</v>
+        <v>0.1647154975189589</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9577975473342335</v>
+        <v>0.9577356803254408</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2091,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.05122561371632558</v>
+        <v>-0.05121983258436367</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1055959012379951</v>
+        <v>0.1055955206149397</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2581897770578444</v>
+        <v>-0.2581832499184022</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1557385496251933</v>
+        <v>0.1557435847496749</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6275984125035574</v>
+        <v>0.6276360061210502</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2116,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1108286684308805</v>
+        <v>-0.1108267148186618</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1140937462761546</v>
+        <v>0.1140925913893564</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3344483019933945</v>
+        <v>-0.3344440848446451</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1127909651316334</v>
+        <v>0.1127906552073214</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3313578400077083</v>
+        <v>0.3313614690628744</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2141,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01220396724800431</v>
+        <v>-0.01219461160179043</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1180185229028871</v>
+        <v>0.1180171835784837</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2435160216462785</v>
+        <v>-0.2435040409724704</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2191080871502699</v>
+        <v>0.2191148177688895</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9176397829023986</v>
+        <v>0.9177017657144886</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2166,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09048136114066326</v>
+        <v>0.09046583737094305</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1120837691629425</v>
+        <v>0.1120843506052636</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1291987896702052</v>
+        <v>-0.1292154530459339</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3101615119515317</v>
+        <v>0.31014712778782</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4195135299990498</v>
+        <v>0.4195957247448671</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2191,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.04579550992862566</v>
+        <v>-0.04573908222075785</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03909742692383593</v>
+        <v>0.03909044840297101</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.1224250585875307</v>
+        <v>-0.1223549532301023</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0308340387302794</v>
+        <v>0.03087678878858661</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2414710814149321</v>
+        <v>0.2419674343520269</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2212,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.01832790500755673</v>
+        <v>-0.009995929077671184</v>
       </c>
       <c r="C31" t="n">
-        <v>0.07641092741851577</v>
+        <v>0.006231377260105819</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1680905707731518</v>
+        <v>-0.02220920408156047</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1314347607580383</v>
+        <v>0.002217345926218101</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8104389944348603</v>
+        <v>0.1086857585213954</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2237,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>baseline_workload</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4536514594486488</v>
+        <v>-0.02241536051837766</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03633543277518615</v>
+        <v>0.01594813274020862</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3824353198466076</v>
+        <v>-0.05367312630985065</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5248675990506899</v>
+        <v>0.008842405273095322</v>
       </c>
       <c r="F32" t="n">
-        <v>9.003178021298596e-36</v>
+        <v>0.1598678058167845</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2262,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.009996935471112977</v>
+        <v>0.005570728378246272</v>
       </c>
       <c r="C33" t="n">
-        <v>0.006231431833130268</v>
+        <v>0.005006929640835368</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.02221031743616471</v>
+        <v>-0.004242673390917117</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002216446493938757</v>
+        <v>0.01538413014740966</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1086532664978554</v>
+        <v>0.2658786763201076</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2291,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.0009841142683511374</v>
+        <v>-0.0009827230356813815</v>
       </c>
       <c r="C34" t="n">
-        <v>0.005676324387152115</v>
+        <v>0.005676341002920121</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.01210950563173568</v>
+        <v>-0.01210814696537279</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0101412770950334</v>
+        <v>0.01014270089401003</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8623592324210245</v>
+        <v>0.862552274488082</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2312,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.0224114700350764</v>
+        <v>0.4536489217528534</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0159480221829158</v>
+        <v>0.03633658329645973</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.05366901913823723</v>
+        <v>0.3824305271705526</v>
       </c>
       <c r="E35" t="n">
-        <v>0.008846079068084434</v>
+        <v>0.5248673163351543</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1599374102620077</v>
+        <v>9.055948133242013e-36</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2337,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.00557057342217894</v>
+        <v>-0.01834482073950132</v>
       </c>
       <c r="C36" t="n">
-        <v>0.005006598757322847</v>
+        <v>0.07640876400843513</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.00424217982721683</v>
+        <v>-0.1681032462992545</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01538332667157471</v>
+        <v>0.1314136048202519</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2658603809065224</v>
+        <v>0.8102621036986019</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2343,7 +2370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,13 +2402,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802939</v>
+        <v>-2.71340732215842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981503</v>
+        <v>0.5044376034036602</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768273511e-08</v>
+        <v>7.486982883651917e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2391,13 +2418,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02522051520904548</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033998</v>
+        <v>0.1001657906734903</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.8012051561485706</v>
       </c>
     </row>
     <row r="4">
@@ -2407,13 +2434,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2243950733516432</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442915</v>
+        <v>0.2334051881144238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069162</v>
+        <v>0.3363525367569152</v>
       </c>
     </row>
     <row r="5">
@@ -2423,13 +2450,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8152523591729706</v>
       </c>
       <c r="C5" t="n">
-        <v>0.173402651392118</v>
+        <v>0.1732905987053341</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054386e-06</v>
+        <v>2.544403764026902e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2466,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387308</v>
+        <v>0.0352966250974221</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919544</v>
+        <v>0.1917359483069558</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713548</v>
+        <v>0.8539430379367475</v>
       </c>
     </row>
     <row r="7">
@@ -2455,13 +2482,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2770307728862447</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133385</v>
+        <v>0.1900876275228708</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125523</v>
+        <v>0.1450102574315859</v>
       </c>
     </row>
     <row r="8">
@@ -2471,13 +2498,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.1033222461364251</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982444</v>
+        <v>0.1951486965374491</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432469</v>
+        <v>0.5964905887803365</v>
       </c>
     </row>
     <row r="9">
@@ -2487,13 +2514,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8739030378849019</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409139</v>
+        <v>0.169537988877078</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342821e-07</v>
+        <v>2.541527320496839e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2530,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0445652077261707</v>
+        <v>-0.04298175525170756</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171632</v>
+        <v>0.2597533292652194</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517843</v>
+        <v>0.8685729341423547</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2546,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798146</v>
+        <v>-0.2734774183375257</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465067</v>
+        <v>0.2785592488643233</v>
       </c>
       <c r="D11" t="n">
-        <v>0.326113242387764</v>
+        <v>0.3262197079678821</v>
       </c>
     </row>
     <row r="12">
@@ -2535,13 +2562,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118148</v>
+        <v>0.08217580196393701</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097172</v>
+        <v>0.2587287215011222</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.7507779355278756</v>
       </c>
     </row>
     <row r="13">
@@ -2551,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.03995788006654503</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743774</v>
+        <v>0.2568297818201686</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123743</v>
+        <v>0.8763631618417496</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2594,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307935</v>
+        <v>-0.05219347665549006</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588724</v>
+        <v>0.2603443755509282</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375534</v>
+        <v>0.8411062907988991</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1183975653249731</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577187</v>
+        <v>0.2570359266688502</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6460556128984086</v>
+        <v>0.6450665788994052</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2626,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379481</v>
+        <v>-0.002815011182394212</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311192</v>
+        <v>0.2376522981116141</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655132</v>
+        <v>0.99054921220034</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2642,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395306</v>
+        <v>0.1056709152111883</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421759</v>
+        <v>0.2542906688395367</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677652912256731</v>
+        <v>0.6777380893434579</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2658,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733254</v>
+        <v>-0.1371135645044839</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313636</v>
+        <v>0.2634072330241227</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546282</v>
+        <v>0.6026884109023538</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2674,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223237</v>
+        <v>-0.02475228489410896</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538116</v>
+        <v>0.2524092973060097</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966677</v>
+        <v>0.921881411996966</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2690,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376411</v>
+        <v>-0.07246351166486088</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541021</v>
+        <v>0.2666987121614955</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222787</v>
+        <v>0.785848458322071</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2706,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305062</v>
+        <v>0.2068090257965716</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450728</v>
+        <v>0.2439533267288642</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719854</v>
+        <v>0.396582710065293</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2722,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362028</v>
+        <v>-0.1686288808585495</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269674845496591</v>
+        <v>0.2694061394634709</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806365</v>
+        <v>0.5313620833011155</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2738,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.4997770753001369</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445716</v>
+        <v>0.2864601345898815</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517186</v>
+        <v>0.0810431355154885</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2754,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9365913375115045</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1483430409733375</v>
+        <v>0.1482811706186312</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.678649464267751e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2743,13 +2770,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5782787024565067</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1145314111910345</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103854e-07</v>
+        <v>4.439337879296806e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2786,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441742</v>
+        <v>0.2379613006187489</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377481</v>
+        <v>0.1503209475356383</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757815</v>
+        <v>0.1134165507753401</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2802,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998643</v>
+        <v>-0.04352683570925961</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386415</v>
+        <v>0.1612096759797174</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400221</v>
+        <v>0.7871591884734995</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2818,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975739</v>
+        <v>-0.07467572557157227</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223571</v>
+        <v>0.16142900261598</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120158</v>
+        <v>0.6436570199176108</v>
       </c>
     </row>
     <row r="29">
@@ -2807,93 +2834,109 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09777326958921141</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290169</v>
+        <v>0.1543602583723146</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510021</v>
+        <v>0.5264661972233924</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2280638724458788</v>
+        <v>-0.004998614827289053</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.008307994570919623</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04668969945129902</v>
+        <v>0.5473983322894245</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962181</v>
+        <v>-0.004172683243731354</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454899</v>
+        <v>0.022235269457398</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341518</v>
+        <v>0.8511427450377176</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002418133412192865</v>
+        <v>0.006367932838418623</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007135781003458533</v>
+        <v>0.006881672701727242</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7347043603418282</v>
+        <v>0.3547856158497279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004129656026475429</v>
+        <v>-0.002450883409209243</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02222260881033176</v>
+        <v>0.007127711187841286</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8525770672961277</v>
+        <v>0.7309569941465313</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_workload</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474494</v>
+        <v>0.01034291492939458</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197173</v>
+        <v>0.05138615505935833</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666431</v>
+        <v>0.8404810151443453</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>is_new_manager</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.227565038115018</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1144549283876819</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.04678402178782413</v>
       </c>
     </row>
   </sheetData>
